--- a/Convert_from_xlsx_to_Json/table_normalization/employment-table02.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/employment-table02.xlsx
@@ -126,12 +126,12 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -445,53 +445,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="3" t="s">
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2" t="s">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2" t="s">
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
     </row>
     <row r="3" spans="1:11" ht="47" customHeight="1">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="4" t="s">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="5" t="s">
@@ -503,13 +503,13 @@
       <c r="H3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="2"/>
+      <c r="K3" s="3"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
@@ -3397,17 +3397,17 @@
       </c>
     </row>
     <row r="91" spans="1:11">
-      <c r="A91" s="1"/>
-      <c r="B91" s="1"/>
-      <c r="C91" s="1"/>
-      <c r="D91" s="1"/>
-      <c r="E91" s="1"/>
-      <c r="F91" s="1"/>
-      <c r="G91" s="1"/>
-      <c r="H91" s="1"/>
-      <c r="I91" s="1"/>
-      <c r="J91" s="1"/>
-      <c r="K91" s="1"/>
+      <c r="A91" s="2"/>
+      <c r="B91" s="2"/>
+      <c r="C91" s="2"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="2"/>
+      <c r="F91" s="2"/>
+      <c r="G91" s="2"/>
+      <c r="H91" s="2"/>
+      <c r="I91" s="2"/>
+      <c r="J91" s="2"/>
+      <c r="K91" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="9">
